--- a/outputs/evaluation/decision/v2/CF_M08/run_3/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_3/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333</v>
+        <v>0.625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667</v>
+        <v>0.3571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8817</v>
+        <v>0.8295</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1667</v>
+        <v>0.3571</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,11 +979,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8752</v>
+        <v>0.7851</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1003,84 +1003,81 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Next.js supports both client-side rendering (CSR) and server-side rendering (SSR), allowing to choose the best strategy according to the needs of the application.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_03, Security</t>
+          <t>C_01, C_06</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_02, AU_23, AU_24</t>
+          <t>AU_03, AU_06</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C15</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8881</v>
+        <v>0.7936</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1107,40 +1104,295 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>AU_08, AU_04</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>*CF_M08_C24</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or the inefficient use of resources.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C_04</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>CF_M08_C06</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M08_P05</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9946</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C_02, C_05</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8881</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C_04, Robustness</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>R_22, C_04</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>AU_02, AU_05</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_C08, *CF_M08_C09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="U6" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1155,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1223,32 +1475,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6187</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects... When the state of the subject changes, it notifies automatically all its observers, allowing that these react appropriately.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_05, Maintainability</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1258,81 +1510,46 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7336</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
+          <t>Docker is a containerization platform used to manage the execution of the application services.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_06, Adaptability</t>
+          <t>C_05, Maintainability</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5961</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_05, Maintainability</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6387</v>
+        <v>0.6791</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,22 +1606,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1412,60 +1630,60 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8749</v>
+        <v>0.7348</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M08_C14</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.584</v>
+        <v>0.6052</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M08_C15</t>
+          <t>*CF_M08_C14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1482,7 +1700,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="5">
@@ -1511,11 +1729,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6473</v>
+        <v>0.6556</v>
       </c>
     </row>
     <row r="6">
@@ -1643,11 +1861,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.653</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="10">
@@ -1676,44 +1894,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.5518999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M08_C24</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7723</v>
       </c>
     </row>
   </sheetData>
